--- a/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
+++ b/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\painani\trunk\recursos\formatos_layout\formato_layout_oficios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\painani\trunk\recursos\formatos_layout\formato_layout_num_oficios\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -138,6 +138,15 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -422,10 +431,12 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
-    <col min="3" max="5" width="17.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="35" style="2" customWidth="1"/>
     <col min="8" max="8" width="48" style="2" customWidth="1"/>
   </cols>
@@ -446,7 +457,7 @@
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -472,7 +483,7 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="3" t="s">

--- a/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
+++ b/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Oficios" sheetId="1" r:id="rId1"/>
+    <sheet name="Prioridades" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>FECHA OFICIO</t>
   </si>
@@ -47,20 +48,38 @@
     <t>NUM. OFICIO</t>
   </si>
   <si>
-    <t>ID BLOQUE</t>
-  </si>
-  <si>
-    <t>ID INSUMO</t>
-  </si>
-  <si>
-    <t>MONTO PRESUNTIVA</t>
+    <t>CODIGO</t>
+  </si>
+  <si>
+    <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t>NIVEL_A</t>
+  </si>
+  <si>
+    <t>Nivel A</t>
+  </si>
+  <si>
+    <t>NIVEL_B</t>
+  </si>
+  <si>
+    <t>Nivel B</t>
+  </si>
+  <si>
+    <t>NIVEL_C</t>
+  </si>
+  <si>
+    <t>Nivel C</t>
+  </si>
+  <si>
+    <t>CODIGO_PRIORIDAD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +101,13 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -125,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -139,20 +165,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="22"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="22"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="22"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="22"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -163,6 +234,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:B4"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="CODIGO" dataDxfId="3"/>
+    <tableColumn id="2" name="DESCRIPCION" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,20 +510,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35" style="2" customWidth="1"/>
-    <col min="8" max="8" width="48" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="2" customWidth="1"/>
+    <col min="6" max="6" width="48" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -452,22 +532,16 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -483,13 +557,7 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -497,4 +565,54 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
+++ b/trunk/recursos/formatos_layout/formato_layout_num_oficios/FORMATO_LAYOUT_OFICIOS.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>FECHA OFICIO</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>NUM. ORDEN</t>
-  </si>
-  <si>
-    <t>NUM. OFICIO</t>
   </si>
   <si>
     <t>CODIGO</t>
@@ -237,11 +234,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:B4" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="A1:B4"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="CODIGO" dataDxfId="3"/>
-    <tableColumn id="2" name="DESCRIPCION" dataDxfId="2"/>
+    <tableColumn id="1" name="CODIGO" dataDxfId="1"/>
+    <tableColumn id="2" name="DESCRIPCION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -510,54 +507,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35" style="2" customWidth="1"/>
-    <col min="6" max="6" width="48" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35" style="2" customWidth="1"/>
+    <col min="5" max="5" width="48" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -578,34 +568,34 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
